--- a/artfynd/A 36910-2024 artfynd.xlsx
+++ b/artfynd/A 36910-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103087038</v>
+        <v>103086974</v>
       </c>
       <c r="B2" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571136.56820549</v>
+        <v>571002</v>
       </c>
       <c r="R2" t="n">
-        <v>7105811.102868643</v>
+        <v>7105482</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,19 +746,9 @@
           <t>2022-08-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,16 +779,11 @@
         <v>103087042</v>
       </c>
       <c r="B3" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571136.56820549</v>
+        <v>571137</v>
       </c>
       <c r="R3" t="n">
-        <v>7105811.102868643</v>
+        <v>7105811</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -867,19 +847,9 @@
           <t>2022-08-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103086997</v>
+        <v>103086979</v>
       </c>
       <c r="B4" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,13 +915,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571043.5180753013</v>
+        <v>571002</v>
       </c>
       <c r="R4" t="n">
-        <v>7105509.040750436</v>
+        <v>7105482</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,19 +948,9 @@
           <t>2022-08-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103087054</v>
+        <v>103086784</v>
       </c>
       <c r="B5" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571083.4652957922</v>
+        <v>570921</v>
       </c>
       <c r="R5" t="n">
-        <v>7105679.409187777</v>
+        <v>7105385</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,19 +1049,9 @@
           <t>2022-08-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103087021</v>
+        <v>103086997</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571134.8155151269</v>
+        <v>571044</v>
       </c>
       <c r="R6" t="n">
-        <v>7105811.062743716</v>
+        <v>7105509</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1215,19 +1150,9 @@
           <t>2022-08-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103087002</v>
+        <v>103087038</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571043.5180753013</v>
+        <v>571137</v>
       </c>
       <c r="R7" t="n">
-        <v>7105509.040750436</v>
+        <v>7105811</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1331,19 +1251,9 @@
           <t>2022-08-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103087007</v>
+        <v>103087054</v>
       </c>
       <c r="B8" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1414,13 +1319,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571043.5180753013</v>
+        <v>571083</v>
       </c>
       <c r="R8" t="n">
-        <v>7105509.040750436</v>
+        <v>7105680</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,19 +1352,9 @@
           <t>2022-08-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,6 +1379,410 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>103086838</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hocksjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>570921</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7105385</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bodum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>103087002</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hocksjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>571044</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7105509</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bodum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>103087021</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hocksjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>571135</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7105811</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bodum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>103087007</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hocksjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>571044</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7105509</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bodum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36910-2024 artfynd.xlsx
+++ b/artfynd/A 36910-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103086974</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103087042</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103086979</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103086784</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103086997</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103087038</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103087054</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103086838</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103087002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103087021</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,8 +1838,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103087007</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>